--- a/tabtools/demo/demo_table1.xlsx
+++ b/tabtools/demo/demo_table1.xlsx
@@ -14,9 +14,9 @@
     <sheet name="Table 1 Formats" sheetId="6" r:id="rId8"/>
     <sheet name="Table 1 Missing" sheetId="7" r:id="rId9"/>
     <sheet name="Table 1 Custom" sheetId="8" r:id="rId10"/>
-    <sheet name="Table 1 NEJM" sheetId="9" r:id="rId11"/>
-    <sheet name="Theme BMJ" sheetId="10" r:id="rId12"/>
-    <sheet name="Theme APA" sheetId="11" r:id="rId13"/>
+    <sheet name="Table 1 Compact" sheetId="9" r:id="rId11"/>
+    <sheet name="Explicit Arial" sheetId="10" r:id="rId12"/>
+    <sheet name="Explicit Serif" sheetId="11" r:id="rId13"/>
     <sheet name="Small Cells Primary" sheetId="12" r:id="rId14"/>
     <sheet name="Small Cells Complement" sheetId="13" r:id="rId15"/>
     <sheet name="Small Cells Binary" sheetId="14" r:id="rId16"/>
@@ -763,13 +763,13 @@
     <t>SD shown as mean [SD]. IQR uses 'to' separator. Row % for categoricals.</t>
   </si>
   <si>
-    <t>Table 1. Baseline Characteristics (NEJM Style)</t>
-  </si>
-  <si>
-    <t>Table 1. Baseline Characteristics (BMJ Style)</t>
-  </si>
-  <si>
-    <t>Table 1. Baseline Characteristics (APA Style)</t>
+    <t>Table 1. Baseline Characteristics (Compact Style)</t>
+  </si>
+  <si>
+    <t>Table 1. Baseline Characteristics (Arial Style)</t>
+  </si>
+  <si>
+    <t>Table 1. Baseline Characteristics (Serif Style)</t>
   </si>
   <si>
     <t>Small-cell suppression: primary counts only</t>

--- a/tabtools/demo/demo_table1.xlsx
+++ b/tabtools/demo/demo_table1.xlsx
@@ -3563,10 +3563,10 @@
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
     <col min="2" max="2" width="26.7109375" style="1" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" style="1" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" style="1" customWidth="true"/>
-    <col min="5" max="5" width="14.7109375" style="1" customWidth="true"/>
-    <col min="6" max="6" width="14.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" style="1" customWidth="true"/>
+    <col min="6" max="6" width="12.7109375" style="1" customWidth="true"/>
     <col min="7" max="7" width="8.7109375" style="1" customWidth="true"/>
   </cols>
   <sheetData>
@@ -4057,8 +4057,8 @@
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
     <col min="2" max="2" width="43.11328125" style="1" customWidth="true"/>
-    <col min="3" max="3" width="13.7109375" style="1" customWidth="true"/>
-    <col min="4" max="4" width="13.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="true"/>
     <col min="7" max="7" width="10.7109375" style="1" customWidth="true"/>
     <col min="5" max="5" width="23.7109375" style="1" customWidth="true"/>
     <col min="6" max="6" width="15.7109375" style="1" customWidth="true"/>
@@ -5072,8 +5072,8 @@
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
     <col min="2" max="2" width="42.51171875" style="1" customWidth="true"/>
-    <col min="3" max="3" width="13.7109375" style="1" customWidth="true"/>
-    <col min="4" max="4" width="13.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="true"/>
     <col min="5" max="5" width="10.7109375" style="1" customWidth="true"/>
   </cols>
   <sheetData>
